--- a/Project_ETF/ETF_Investment_Portfolio/009819/ETF_Investment_Portfolio_20260824.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/009819/ETF_Investment_Portfolio_20260824.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D52"/>
+  <dimension ref="A1:D53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24.75" customWidth="1" min="1" max="1"/>
@@ -611,12 +611,12 @@
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>130,785</t>
+          <t>131,735</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>27.00%</t>
+          <t>26.64%</t>
         </is>
       </c>
     </row>
@@ -633,12 +633,12 @@
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>14,925</t>
+          <t>15,025</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>8.00%</t>
+          <t>7.99%</t>
         </is>
       </c>
     </row>
@@ -655,12 +655,12 @@
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>94,830</t>
+          <t>95,630</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>7.78%</t>
+          <t>7.69%</t>
         </is>
       </c>
     </row>
@@ -677,12 +677,12 @@
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>48,315</t>
+          <t>48,665</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>6.42%</t>
+          <t>6.29%</t>
         </is>
       </c>
     </row>
@@ -699,56 +699,56 @@
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>115,295</t>
+          <t>116,145</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>5.40%</t>
+          <t>5.51%</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>NOW US</t>
+          <t>C_NTD</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>ServiceNow Inc</t>
+          <t>CASH</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>56,740</t>
+          <t>245,441,045</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>4.08%</t>
+          <t>4.34%</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>C_NTD</t>
+          <t>NOW US</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>CASH</t>
+          <t>ServiceNow Inc</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>213,059,099</t>
+          <t>57,140</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>3.75%</t>
+          <t>4.13%</t>
         </is>
       </c>
     </row>
@@ -787,12 +787,12 @@
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>62,305</t>
+          <t>62,735</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>3.11%</t>
+          <t>3.19%</t>
         </is>
       </c>
     </row>
@@ -809,12 +809,12 @@
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>42,915</t>
+          <t>43,265</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>2.88%</t>
+          <t>2.98%</t>
         </is>
       </c>
     </row>
@@ -831,12 +831,12 @@
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>18,785</t>
+          <t>18,915</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>2.87%</t>
+          <t>2.92%</t>
         </is>
       </c>
     </row>
@@ -853,12 +853,12 @@
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>17,353</t>
+          <t>17,513</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>2.85%</t>
+          <t>2.77%</t>
         </is>
       </c>
     </row>
@@ -875,56 +875,56 @@
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>73,045</t>
+          <t>73,645</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>2.19%</t>
+          <t>2.18%</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>DLR US</t>
+          <t>AEP US</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>數位不動產信託公司</t>
+          <t>美國電力公司</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>19,345</t>
+          <t>30,180</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>2.07%</t>
+          <t>2.08%</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>AEP US</t>
+          <t>DLR US</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>美國電力公司</t>
+          <t>數位不動產信託公司</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>29,970</t>
+          <t>19,465</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>2.03%</t>
+          <t>2.07%</t>
         </is>
       </c>
     </row>
@@ -941,12 +941,12 @@
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>48,645</t>
+          <t>48,945</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>1.82%</t>
+          <t>1.84%</t>
         </is>
       </c>
     </row>
@@ -963,12 +963,12 @@
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>25,228</t>
+          <t>25,398</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>1.48%</t>
+          <t>1.52%</t>
         </is>
       </c>
     </row>
@@ -985,12 +985,12 @@
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>34,430</t>
+          <t>34,670</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>1.47%</t>
+          <t>1.51%</t>
         </is>
       </c>
     </row>
@@ -1007,12 +1007,12 @@
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>18,490</t>
+          <t>18,620</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>1.41%</t>
+          <t>1.43%</t>
         </is>
       </c>
     </row>
@@ -1029,12 +1029,12 @@
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>56,508</t>
+          <t>56,898</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>1.39%</t>
+          <t>1.42%</t>
         </is>
       </c>
     </row>
@@ -1056,7 +1056,7 @@
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>1.37%</t>
+          <t>1.33%</t>
         </is>
       </c>
     </row>
@@ -1073,51 +1073,51 @@
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>20,298</t>
+          <t>20,438</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>1.21%</t>
+          <t>1.24%</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>ALAB US</t>
+          <t>PCG US</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>Astera實驗室公司</t>
+          <t>太平洋電力瓦斯公司</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>7,590</t>
+          <t>121,715</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>1.21%</t>
+          <t>1.24%</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>PCG US</t>
+          <t>ALAB US</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>太平洋電力瓦斯公司</t>
+          <t>Astera實驗室公司</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>120,885</t>
+          <t>7,590</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>9,136</t>
+          <t>9,236</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>1.18%</t>
+          <t>1.16%</t>
         </is>
       </c>
     </row>
@@ -1161,29 +1161,29 @@
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>17,525</t>
+          <t>17,645</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>1.04%</t>
+          <t>1.07%</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>CRWV US</t>
+          <t>AEE US</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>CoreWeave Inc</t>
+          <t>阿莫林公司</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>18,637</t>
+          <t>15,171</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
@@ -1195,22 +1195,22 @@
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>AEE US</t>
+          <t>CRWV US</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>阿莫林公司</t>
+          <t>CoreWeave Inc</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>15,071</t>
+          <t>18,767</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>0.90%</t>
+          <t>0.91%</t>
         </is>
       </c>
     </row>
@@ -1227,12 +1227,12 @@
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>41,210</t>
+          <t>41,490</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>0.79%</t>
+          <t>0.82%</t>
         </is>
       </c>
     </row>
@@ -1249,12 +1249,12 @@
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>35,730</t>
+          <t>35,980</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>0.78%</t>
+          <t>0.79%</t>
         </is>
       </c>
     </row>
@@ -1271,7 +1271,7 @@
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>11,215</t>
+          <t>11,315</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
@@ -1299,6 +1299,28 @@
       <c r="D52" s="4" t="inlineStr">
         <is>
           <t>0.39%</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="3" t="inlineStr">
+        <is>
+          <t>RDI_USD</t>
+        </is>
+      </c>
+      <c r="B53" s="3" t="inlineStr">
+        <is>
+          <t>RECEIVABLES FOR DISPOSAL OF INVESTMENTS</t>
+        </is>
+      </c>
+      <c r="C53" s="4" t="inlineStr">
+        <is>
+          <t>-205,833</t>
+        </is>
+      </c>
+      <c r="D53" s="4" t="inlineStr">
+        <is>
+          <t>0.00%</t>
         </is>
       </c>
     </row>
